--- a/Connection_Tracker.xlsx
+++ b/Connection_Tracker.xlsx
@@ -8,15 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E8742A-7FB2-4432-96C2-45A9CBF07234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC98C09-665B-439F-985F-BB8942569A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker" sheetId="1" r:id="rId1"/>
     <sheet name="Settings" sheetId="2" r:id="rId2"/>
-    <sheet name="Read Me" sheetId="3" r:id="rId3"/>
+    <sheet name="Email Log" sheetId="3" r:id="rId3"/>
+    <sheet name="Read Me" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="OfficerList">Settings!$D$2:$D$50</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -35,15 +39,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="108">
   <si>
     <t>WBS No. / SQ No.</t>
   </si>
   <si>
-    <t>Customer / Project Name</t>
-  </si>
-  <si>
-    <t>Application Type</t>
+    <t>Customer</t>
   </si>
   <si>
     <t>Planning Officer</t>
@@ -52,31 +53,34 @@
     <t>Officer Email</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Last Status Change</t>
-  </si>
-  <si>
-    <t>SLA Days</t>
-  </si>
-  <si>
-    <t>Days Pending</t>
-  </si>
-  <si>
-    <t>Days vs SLA</t>
+    <t>Conn. Charge Paid</t>
+  </si>
+  <si>
+    <t>Conn. Paid Date</t>
+  </si>
+  <si>
+    <t>Other Charge Status</t>
+  </si>
+  <si>
+    <t>Target Date</t>
+  </si>
+  <si>
+    <t>Days vs Target</t>
   </si>
   <si>
     <t>Submission Round</t>
   </si>
   <si>
-    <t>Paid</t>
-  </si>
-  <si>
-    <t>Paid Date</t>
-  </si>
-  <si>
-    <t>Budget Assigned</t>
+    <t>Rejection Reason</t>
+  </si>
+  <si>
+    <t>Snooze Until</t>
+  </si>
+  <si>
+    <t>Finance Reminders</t>
+  </si>
+  <si>
+    <t>Last Reminder Date</t>
   </si>
   <si>
     <t>Priority</t>
@@ -85,184 +89,280 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>SIB-260001</t>
-  </si>
-  <si>
-    <t>Example A - Housing Ph2</t>
-  </si>
-  <si>
-    <t>Turnkey Stage 2</t>
+    <t>SIB-260101</t>
+  </si>
+  <si>
+    <t>Alpha Housing</t>
   </si>
   <si>
     <t>ABC</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>1st</t>
+  </si>
+  <si>
+    <t>Paid - other charge not listed yet (EXAMPLE)</t>
+  </si>
+  <si>
+    <t>SIB-260102</t>
+  </si>
+  <si>
+    <t>Beta Supply</t>
+  </si>
+  <si>
+    <t>DEF</t>
+  </si>
+  <si>
+    <t>Rejected - Pending Resubmission</t>
+  </si>
+  <si>
+    <t>2nd</t>
+  </si>
+  <si>
+    <t>Missing cable schedule</t>
+  </si>
+  <si>
+    <t>Rejected, 8 days past target (EXAMPLE)</t>
+  </si>
+  <si>
+    <t>SIB-260103</t>
+  </si>
+  <si>
+    <t>Gamma Lot</t>
+  </si>
+  <si>
+    <t>GHI</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Awaiting connection charge payment (EXAMPLE)</t>
+  </si>
+  <si>
+    <t>SIB-260104</t>
+  </si>
+  <si>
+    <t>Delta Works</t>
+  </si>
+  <si>
+    <t>JKL</t>
+  </si>
+  <si>
+    <t>Pending Engineer</t>
+  </si>
+  <si>
+    <t>With engineer, due tomorrow (EXAMPLE)</t>
+  </si>
+  <si>
+    <t>SIB-260105</t>
+  </si>
+  <si>
+    <t>Epsilon Depot</t>
+  </si>
+  <si>
+    <t>MNO</t>
+  </si>
+  <si>
+    <t>Pending Manager</t>
+  </si>
+  <si>
+    <t>With manager, 3 days overdue (EXAMPLE)</t>
+  </si>
+  <si>
+    <t>SIB-260106</t>
+  </si>
+  <si>
+    <t>Zeta Plaza</t>
+  </si>
+  <si>
+    <t>PQR</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Done (EXAMPLE)</t>
+  </si>
+  <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Officer</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Escalate - days past target</t>
+  </si>
+  <si>
+    <t>abc@example.com</t>
+  </si>
+  <si>
+    <t>"Due soon" - days before target</t>
+  </si>
+  <si>
+    <t>def@example.com</t>
+  </si>
+  <si>
+    <t>Paid project - chase after (days)</t>
+  </si>
+  <si>
+    <t>ghi@example.com</t>
+  </si>
+  <si>
+    <t>Default officer email (fallback)</t>
+  </si>
+  <si>
     <t>officer@example.com</t>
   </si>
   <si>
-    <t>Rejected - Pending Resubmission</t>
-  </si>
-  <si>
-    <t>2nd</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Paid, budget not yet assigned (EXAMPLE ROW)</t>
-  </si>
-  <si>
-    <t>SIB260002</t>
-  </si>
-  <si>
-    <t>Example B - Kpg Supply</t>
-  </si>
-  <si>
-    <t>Supply Application (&lt;100kW)</t>
-  </si>
-  <si>
-    <t>DEF</t>
-  </si>
-  <si>
-    <t>Cost Submitted</t>
-  </si>
-  <si>
-    <t>1st</t>
-  </si>
-  <si>
-    <t>(EXAMPLE ROW)</t>
-  </si>
-  <si>
-    <t>SQ5401</t>
-  </si>
-  <si>
-    <t>Example C - Commercial Lot</t>
-  </si>
-  <si>
-    <t>Upgrading/Downgrading of Supply</t>
-  </si>
-  <si>
-    <t>GHI</t>
-  </si>
-  <si>
-    <t>Charge Issued</t>
-  </si>
-  <si>
-    <t>Awaiting customer payment (EXAMPLE ROW)</t>
-  </si>
-  <si>
-    <t>SIB-260004</t>
-  </si>
-  <si>
-    <t>Example D - Quarry Access</t>
-  </si>
-  <si>
-    <t>Turnkey Stage 1</t>
-  </si>
-  <si>
-    <t>JKL</t>
-  </si>
-  <si>
-    <t>Keyed into SAP</t>
-  </si>
-  <si>
-    <t>3rd</t>
-  </si>
-  <si>
-    <t>Past SLA, third round (EXAMPLE ROW)</t>
-  </si>
-  <si>
-    <t>Setting</t>
-  </si>
-  <si>
-    <t>Days</t>
-  </si>
-  <si>
-    <t>Paid project - chase after (days pending)</t>
-  </si>
-  <si>
-    <t>"Due soon" warning - days before SLA</t>
-  </si>
-  <si>
-    <t>Escalate - days past SLA</t>
-  </si>
-  <si>
-    <t>Default SLA days (used when SLA Days is blank)</t>
-  </si>
-  <si>
-    <t>Yellow cells are inputs - change these anytime, no flow changes needed.</t>
-  </si>
-  <si>
-    <t>SESCO Planning - Connection Charge Tracker (intern project)</t>
+    <t>jkl@example.com</t>
+  </si>
+  <si>
+    <t>Engineer email</t>
+  </si>
+  <si>
+    <t>engineer@example.com</t>
+  </si>
+  <si>
+    <t>mno@example.com</t>
+  </si>
+  <si>
+    <t>Manager email</t>
+  </si>
+  <si>
+    <t>manager@example.com</t>
+  </si>
+  <si>
+    <t>pqr@example.com</t>
+  </si>
+  <si>
+    <t>Yellow = inputs. Change anytime; scripts read these, no code edit needed.</t>
+  </si>
+  <si>
+    <t>Add an operator by adding a row here. The Tracker's officer dropdown updates.</t>
+  </si>
+  <si>
+    <t>Date/Time</t>
+  </si>
+  <si>
+    <t>Sender</t>
+  </si>
+  <si>
+    <t>Subject</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>Action taken</t>
+  </si>
+  <si>
+    <t>03/08/2026 09:36</t>
+  </si>
+  <si>
+    <t>finance.a@sarawakenergy.com</t>
+  </si>
+  <si>
+    <t>[For Action] CC Bill Paid - SIB-260101</t>
+  </si>
+  <si>
+    <t>Marked paid (EXAMPLE)</t>
+  </si>
+  <si>
+    <t>SESCO Planning - Other Charge Tracker</t>
+  </si>
+  <si>
+    <t>SHEETS</t>
+  </si>
+  <si>
+    <t>Tracker   - one row per project (the Other Charge).</t>
+  </si>
+  <si>
+    <t>Settings  - all variables: thresholds + emails (left) and the Officer directory (right).</t>
+  </si>
+  <si>
+    <t>Email Log - every Finance email the automation processes is logged here.</t>
   </si>
   <si>
     <t>HEADER COLOURS</t>
   </si>
   <si>
-    <t>Dark blue = you fill in.   Green = filled automatically by Power Automate.   Grey = formula, do not type over.</t>
-  </si>
-  <si>
-    <t>PRIORITY (most urgent first)</t>
-  </si>
-  <si>
-    <t>HIGH - ASSIGN BUDGET  (RED) - customer paid, Budget Assigned is not Yes. Money sits in CC-Suspense until done.</t>
-  </si>
-  <si>
-    <t>HIGH - PAID           (RED) - customer has paid. Paid projects are always high priority.</t>
-  </si>
-  <si>
-    <t>OVERDUE - ESCALATE - past SLA by more than the escalation threshold.</t>
-  </si>
-  <si>
-    <t>OVERDUE - past its SLA date.      DUE SOON - approaching its SLA date.</t>
-  </si>
-  <si>
-    <t>AWAITING PAYMENT - charge issued, customer has not paid. No action needed from the team.</t>
-  </si>
-  <si>
-    <t>OK - within SLA.                  SET DATE - Last Status Change is empty, please fill it.</t>
-  </si>
-  <si>
-    <t>NEW ROWS</t>
-  </si>
-  <si>
-    <t>Days Pending, Days vs SLA and Priority are table calculated columns - they fill in automatically</t>
-  </si>
-  <si>
-    <t>when you add a row. Do not type over them.</t>
-  </si>
-  <si>
-    <t>SLA DAYS</t>
-  </si>
-  <si>
-    <t>Mirrors the team sheet's '10/12 days' column. Enter the number governing that project (10, 12 or 14).</t>
-  </si>
-  <si>
-    <t>If left blank, the Settings sheet default is used.</t>
-  </si>
-  <si>
-    <t>ASSUMPTIONS TO CONFIRM</t>
-  </si>
-  <si>
-    <t>1. STA(P) - assumed to be the reviewing party Planning submits to. Nothing here depends on it.</t>
-  </si>
-  <si>
-    <t>2. Confirm what 10/12/14 represent, and whether they are calendar or working days (currently calendar).</t>
-  </si>
-  <si>
-    <t>3. Settings thresholds are placeholders - agree real numbers with the team.</t>
+    <t>Dark blue = you fill in.   Green = set automatically by Power Automate.   Grey = formula, do not type over.</t>
+  </si>
+  <si>
+    <t>OFFICER + EMAIL</t>
+  </si>
+  <si>
+    <t>Pick the Planning Officer from the dropdown; the Officer Email fills in automatically from the</t>
+  </si>
+  <si>
+    <t>Officer directory on the Settings sheet. To add an operator, add a row to that directory.</t>
+  </si>
+  <si>
+    <t>THE DEADLINE - 'Target Date'</t>
+  </si>
+  <si>
+    <t>Each project has a Target Date you set. 'Days vs Target': positive = overdue, negative = days left.</t>
+  </si>
+  <si>
+    <t>WHO GETS CHASED = THE STATUS</t>
+  </si>
+  <si>
+    <t>Not Started (paid) -&gt; Operator.   Keyed into SAP / Pending Engineer -&gt; Engineer.</t>
+  </si>
+  <si>
+    <t>Pending Manager -&gt; Manager.       Rejected - Pending Resubmission -&gt; Operator.</t>
+  </si>
+  <si>
+    <t>Approved / Completed -&gt; nobody (done).</t>
+  </si>
+  <si>
+    <t>PRIORITY MEANINGS (most urgent first)</t>
+  </si>
+  <si>
+    <t>URGENT - LIST CHARGE (red) - paid, other charge still Not Started.</t>
+  </si>
+  <si>
+    <t>OVERDUE - ESCALATE (orange) - past target by the escalation threshold.</t>
+  </si>
+  <si>
+    <t>OVERDUE (amber) - past Target Date.   DUE SOON - approaching it.</t>
+  </si>
+  <si>
+    <t>SNOOZED - a future Snooze Until date is set; silent until then (temporary).</t>
+  </si>
+  <si>
+    <t>DONE - Approved or Completed; never chased again (permanent).</t>
+  </si>
+  <si>
+    <t>SET TARGET - in progress but no Target Date yet.   OK - nothing to do yet.</t>
+  </si>
+  <si>
+    <t>SNOOZE vs DONE</t>
+  </si>
+  <si>
+    <t>Snooze = 'chase me after this date', expires by itself. Done = Status set to Completed/Approved,</t>
+  </si>
+  <si>
+    <t>stops reminders permanently. Both stop the emails; only Snooze comes back on its own.</t>
   </si>
   <si>
     <t>DATA NOTE</t>
   </si>
   <si>
-    <t>All example rows are invented. Delete them before real use.</t>
-  </si>
-  <si>
-    <t>Keep genuine customer data out of anything sent to personal or external accounts.</t>
+    <t>All example rows and addresses are invented. Delete them before real use.</t>
   </si>
 </sst>
 </file>
@@ -272,7 +372,7 @@
   <numFmts count="1">
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -283,11 +383,12 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -296,18 +397,22 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <i/>
       <sz val="9"/>
       <name val="Arial"/>
     </font>
     <font>
+      <i/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -320,22 +425,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E79"/>
+        <fgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF595959"/>
+        <fgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
+        <fgColor rgb="FFC6E0B4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -366,7 +471,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -386,19 +491,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -421,7 +540,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
+          <fgColor rgb="FFA9D08E"/>
         </patternFill>
       </fill>
     </dxf>
@@ -434,7 +553,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFD9E1F2"/>
+          <fgColor rgb="FFB4C7E7"/>
         </patternFill>
       </fill>
     </dxf>
@@ -468,12 +587,12 @@
       <font>
         <b/>
         <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FF000000"/>
         <name val="Arial"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFED7D31"/>
+          <fgColor rgb="FFF4B183"/>
         </patternFill>
       </fill>
     </dxf>
@@ -481,25 +600,12 @@
       <font>
         <b/>
         <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FF000000"/>
         <name val="Arial"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC00000"/>
+          <fgColor rgb="FFFF9999"/>
         </patternFill>
       </fill>
     </dxf>
@@ -522,6 +628,19 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -536,32 +655,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProjectTracker" displayName="ProjectTracker" ref="A1:P5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProjectTracker" displayName="ProjectTracker" ref="A1:P7">
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="WBS No. / SQ No."/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Customer / Project Name"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Application Type"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Planning Officer"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Officer Email"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Status"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Last Status Change"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="SLA Days"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Days Pending">
-      <calculatedColumnFormula>IF($A2="","",IF($G2="","",TODAY()-$G2))</calculatedColumnFormula>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Customer"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Planning Officer"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Officer Email">
+      <calculatedColumnFormula>IF($C2="",Settings!$B$5,IFERROR(INDEX(Settings!$E$2:$E$50,MATCH($C2,Settings!$D$2:$D$50,0)),Settings!$B$5))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Days vs SLA">
-      <calculatedColumnFormula>IF($A2="","",IF($G2="","",$I2-IF($H2="",Settings!$B$5,$H2)))</calculatedColumnFormula>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Conn. Charge Paid"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Conn. Paid Date"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Other Charge Status"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Target Date"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Days vs Target">
+      <calculatedColumnFormula>IF($A2="","",IF($H2="","",TODAY()-$H2))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Submission Round"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Paid"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Paid Date"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Budget Assigned"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Submission Round"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Rejection Reason"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Snooze Until"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Finance Reminders"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Last Reminder Date"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Priority">
-      <calculatedColumnFormula>IF($A2="","",IF($F2="Completed","-",IF($G2="","SET DATE",IF(AND($L2="Yes",$N2&lt;&gt;"Yes"),"HIGH - ASSIGN BUDGET",IF($L2="Yes","HIGH - PAID",IF(AND($F2="Charge Issued",$L2&lt;&gt;"Yes"),"AWAITING PAYMENT",IF($J2&gt;=Settings!$B$4,"OVERDUE - ESCALATE",IF($J2&gt;0,"OVERDUE",IF($J2&gt;=-1*Settings!$B$3,"DUE SOON","OK")))))))))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF($A2="","",IF(OR($G2="Completed",$G2="Approved"),"DONE",IF(AND($L2&lt;&gt;"",$L2&gt;=TODAY()),"SNOOZED",IF(AND($E2="Yes",$G2="Not Started"),"URGENT - LIST CHARGE",IF(AND($E2&lt;&gt;"Yes",$G2="Not Started"),"OK",IF($H2="","SET TARGET",IF($I2&gt;=Settings!$B$2,"OVERDUE - ESCALATE",IF($I2&gt;0,"OVERDUE",IF($I2&gt;=-1*Settings!$B$3,"DUE SOON","OK")))))))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Remarks"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -850,24 +969,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="27" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="8" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="24" customWidth="1"/>
-    <col min="16" max="16" width="34" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="26" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="11" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="15" max="15" width="22" customWidth="1"/>
+    <col min="16" max="16" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -880,13 +1000,13 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -898,19 +1018,19 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="2" t="s">
@@ -930,254 +1050,328 @@
       <c r="C2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="4" t="str">
+        <f>IF($C2="",Settings!$B$5,IFERROR(INDEX(Settings!$E$2:$E$50,MATCH($C2,Settings!$D$2:$D$50,0)),Settings!$B$5))</f>
+        <v>abc@example.com</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="5">
+        <v>46236</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="H2" s="5"/>
+      <c r="I2" s="6" t="str">
+        <f t="shared" ref="I2:I7" ca="1" si="0">IF($A2="","",IF($H2="","",TODAY()-$H2))</f>
+        <v/>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="5">
-        <v>46231</v>
-      </c>
-      <c r="H2" s="4">
-        <v>10</v>
-      </c>
-      <c r="I2" s="6">
-        <f ca="1">IF($A2="","",IF($G2="","",TODAY()-$G2))</f>
-        <v>6</v>
-      </c>
-      <c r="J2" s="6">
-        <f ca="1">IF($A2="","",IF($G2="","",$I2-IF($H2="",Settings!$B$5,$H2)))</f>
-        <v>-4</v>
-      </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="4"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
+      <c r="N2" s="5"/>
+      <c r="O2" s="7" t="str">
+        <f ca="1">IF($A2="","",IF(OR($G2="Completed",$G2="Approved"),"DONE",IF(AND($L2&lt;&gt;"",$L2&gt;=TODAY()),"SNOOZED",IF(AND($E2="Yes",$G2="Not Started"),"URGENT - LIST CHARGE",IF(AND($E2&lt;&gt;"Yes",$G2="Not Started"),"OK",IF($H2="","SET TARGET",IF($I2&gt;=Settings!$B$2,"OVERDUE - ESCALATE",IF($I2&gt;0,"OVERDUE",IF($I2&gt;=-1*Settings!$B$3,"DUE SOON","OK")))))))))</f>
+        <v>URGENT - LIST CHARGE</v>
+      </c>
+      <c r="P2" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" s="5">
-        <v>46233</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" s="7" t="str">
-        <f>IF($A2="","",IF($F2="Completed","-",IF($G2="","SET DATE",IF(AND($L2="Yes",$N2&lt;&gt;"Yes"),"HIGH - ASSIGN BUDGET",IF($L2="Yes","HIGH - PAID",IF(AND($F2="Charge Issued",$L2&lt;&gt;"Yes"),"AWAITING PAYMENT",IF($J2&gt;=Settings!$B$4,"OVERDUE - ESCALATE",IF($J2&gt;0,"OVERDUE",IF($J2&gt;=-1*Settings!$B$3,"DUE SOON","OK")))))))))</f>
-        <v>HIGH - ASSIGN BUDGET</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="4" t="str">
+        <f>IF($C3="",Settings!$B$5,IFERROR(INDEX(Settings!$E$2:$E$50,MATCH($C3,Settings!$D$2:$D$50,0)),Settings!$B$5))</f>
+        <v>def@example.com</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="5">
+        <v>46219</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="H3" s="5">
+        <v>46231</v>
+      </c>
+      <c r="I3" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="L3" s="5"/>
+      <c r="M3" s="4">
+        <v>2</v>
+      </c>
+      <c r="N3" s="5">
+        <v>46237</v>
+      </c>
+      <c r="O3" s="7" t="str">
+        <f ca="1">IF($A3="","",IF(OR($G3="Completed",$G3="Approved"),"DONE",IF(AND($L3&lt;&gt;"",$L3&gt;=TODAY()),"SNOOZED",IF(AND($E3="Yes",$G3="Not Started"),"URGENT - LIST CHARGE",IF(AND($E3&lt;&gt;"Yes",$G3="Not Started"),"OK",IF($H3="","SET TARGET",IF($I3&gt;=Settings!$B$2,"OVERDUE - ESCALATE",IF($I3&gt;0,"OVERDUE",IF($I3&gt;=-1*Settings!$B$3,"DUE SOON","OK")))))))))</f>
+        <v>OVERDUE - ESCALATE</v>
+      </c>
+      <c r="P3" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="5">
-        <v>46236</v>
-      </c>
-      <c r="H3" s="4">
-        <v>12</v>
-      </c>
-      <c r="I3" s="6">
-        <f ca="1">IF($A3="","",IF($G3="","",TODAY()-$G3))</f>
-        <v>1</v>
-      </c>
-      <c r="J3" s="6">
-        <f ca="1">IF($A3="","",IF($G3="","",$I3-IF($H3="",Settings!$B$5,$H3)))</f>
-        <v>-11</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" s="5"/>
-      <c r="N3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="O3" s="7" t="str">
-        <f ca="1">IF($A3="","",IF($F3="Completed","-",IF($G3="","SET DATE",IF(AND($L3="Yes",$N3&lt;&gt;"Yes"),"HIGH - ASSIGN BUDGET",IF($L3="Yes","HIGH - PAID",IF(AND($F3="Charge Issued",$L3&lt;&gt;"Yes"),"AWAITING PAYMENT",IF($J3&gt;=Settings!$B$4,"OVERDUE - ESCALATE",IF($J3&gt;0,"OVERDUE",IF($J3&gt;=-1*Settings!$B$3,"DUE SOON","OK")))))))))</f>
-        <v>OK</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="4" t="str">
+        <f>IF($C4="",Settings!$B$5,IFERROR(INDEX(Settings!$E$2:$E$50,MATCH($C4,Settings!$D$2:$D$50,0)),Settings!$B$5))</f>
+        <v>ghi@example.com</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="F4" s="5"/>
+      <c r="G4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="6" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5"/>
+      <c r="O4" s="7" t="str">
+        <f ca="1">IF($A4="","",IF(OR($G4="Completed",$G4="Approved"),"DONE",IF(AND($L4&lt;&gt;"",$L4&gt;=TODAY()),"SNOOZED",IF(AND($E4="Yes",$G4="Not Started"),"URGENT - LIST CHARGE",IF(AND($E4&lt;&gt;"Yes",$G4="Not Started"),"OK",IF($H4="","SET TARGET",IF($I4&gt;=Settings!$B$2,"OVERDUE - ESCALATE",IF($I4&gt;0,"OVERDUE",IF($I4&gt;=-1*Settings!$B$3,"DUE SOON","OK")))))))))</f>
+        <v>OK</v>
+      </c>
+      <c r="P4" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="5">
-        <v>46227</v>
-      </c>
-      <c r="H4" s="4">
-        <v>14</v>
-      </c>
-      <c r="I4" s="6">
-        <f ca="1">IF($A4="","",IF($G4="","",TODAY()-$G4))</f>
-        <v>10</v>
-      </c>
-      <c r="J4" s="6">
-        <f ca="1">IF($A4="","",IF($G4="","",$I4-IF($H4="",Settings!$B$5,$H4)))</f>
-        <v>-4</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4" s="5"/>
-      <c r="N4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="O4" s="7" t="str">
-        <f>IF($A4="","",IF($F4="Completed","-",IF($G4="","SET DATE",IF(AND($L4="Yes",$N4&lt;&gt;"Yes"),"HIGH - ASSIGN BUDGET",IF($L4="Yes","HIGH - PAID",IF(AND($F4="Charge Issued",$L4&lt;&gt;"Yes"),"AWAITING PAYMENT",IF($J4&gt;=Settings!$B$4,"OVERDUE - ESCALATE",IF($J4&gt;0,"OVERDUE",IF($J4&gt;=-1*Settings!$B$3,"DUE SOON","OK")))))))))</f>
-        <v>AWAITING PAYMENT</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="4" t="str">
+        <f>IF($C5="",Settings!$B$5,IFERROR(INDEX(Settings!$E$2:$E$50,MATCH($C5,Settings!$D$2:$D$50,0)),Settings!$B$5))</f>
+        <v>jkl@example.com</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="5">
+        <v>46233</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="5">
+        <v>46240</v>
+      </c>
+      <c r="I5" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="4">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5"/>
+      <c r="O5" s="7" t="str">
+        <f ca="1">IF($A5="","",IF(OR($G5="Completed",$G5="Approved"),"DONE",IF(AND($L5&lt;&gt;"",$L5&gt;=TODAY()),"SNOOZED",IF(AND($E5="Yes",$G5="Not Started"),"URGENT - LIST CHARGE",IF(AND($E5&lt;&gt;"Yes",$G5="Not Started"),"OK",IF($H5="","SET TARGET",IF($I5&gt;=Settings!$B$2,"OVERDUE - ESCALATE",IF($I5&gt;0,"OVERDUE",IF($I5&gt;=-1*Settings!$B$3,"DUE SOON","OK")))))))))</f>
+        <v>DUE SOON</v>
+      </c>
+      <c r="P5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="4" t="s">
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="B6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="D6" s="4" t="str">
+        <f>IF($C6="",Settings!$B$5,IFERROR(INDEX(Settings!$E$2:$E$50,MATCH($C6,Settings!$D$2:$D$50,0)),Settings!$B$5))</f>
+        <v>mno@example.com</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="5">
+        <v>46209</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="5">
+        <v>46236</v>
+      </c>
+      <c r="I6" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="4">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5"/>
+      <c r="O6" s="7" t="str">
+        <f ca="1">IF($A6="","",IF(OR($G6="Completed",$G6="Approved"),"DONE",IF(AND($L6&lt;&gt;"",$L6&gt;=TODAY()),"SNOOZED",IF(AND($E6="Yes",$G6="Not Started"),"URGENT - LIST CHARGE",IF(AND($E6&lt;&gt;"Yes",$G6="Not Started"),"OK",IF($H6="","SET TARGET",IF($I6&gt;=Settings!$B$2,"OVERDUE - ESCALATE",IF($I6&gt;0,"OVERDUE",IF($I6&gt;=-1*Settings!$B$3,"DUE SOON","OK")))))))))</f>
+        <v>OVERDUE</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="4" t="str">
+        <f>IF($C7="",Settings!$B$5,IFERROR(INDEX(Settings!$E$2:$E$50,MATCH($C7,Settings!$D$2:$D$50,0)),Settings!$B$5))</f>
+        <v>pqr@example.com</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="5">
+        <v>46199</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="5">
+        <v>46219</v>
+      </c>
+      <c r="I7" s="6">
+        <f t="shared" ca="1" si="0"/>
         <v>20</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G5" s="5">
-        <v>46222</v>
-      </c>
-      <c r="H5" s="4">
-        <v>10</v>
-      </c>
-      <c r="I5" s="6">
-        <f ca="1">IF($A5="","",IF($G5="","",TODAY()-$G5))</f>
-        <v>15</v>
-      </c>
-      <c r="J5" s="6">
-        <f ca="1">IF($A5="","",IF($G5="","",$I5-IF($H5="",Settings!$B$5,$H5)))</f>
-        <v>5</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" s="5"/>
-      <c r="N5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" s="7" t="str">
-        <f ca="1">IF($A5="","",IF($F5="Completed","-",IF($G5="","SET DATE",IF(AND($L5="Yes",$N5&lt;&gt;"Yes"),"HIGH - ASSIGN BUDGET",IF($L5="Yes","HIGH - PAID",IF(AND($F5="Charge Issued",$L5&lt;&gt;"Yes"),"AWAITING PAYMENT",IF($J5&gt;=Settings!$B$4,"OVERDUE - ESCALATE",IF($J5&gt;0,"OVERDUE",IF($J5&gt;=-1*Settings!$B$3,"DUE SOON","OK")))))))))</f>
-        <v>OVERDUE - ESCALATE</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>45</v>
+      <c r="J7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="4">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5"/>
+      <c r="O7" s="7" t="str">
+        <f ca="1">IF($A7="","",IF(OR($G7="Completed",$G7="Approved"),"DONE",IF(AND($L7&lt;&gt;"",$L7&gt;=TODAY()),"SNOOZED",IF(AND($E7="Yes",$G7="Not Started"),"URGENT - LIST CHARGE",IF(AND($E7&lt;&gt;"Yes",$G7="Not Started"),"OK",IF($H7="","SET TARGET",IF($I7&gt;=Settings!$B$2,"OVERDUE - ESCALATE",IF($I7&gt;0,"OVERDUE",IF($I7&gt;=-1*Settings!$B$3,"DUE SOON","OK")))))))))</f>
+        <v>DONE</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="K2:K400">
-    <cfRule type="expression" dxfId="9" priority="9" stopIfTrue="1">
-      <formula>OR($K2="3rd",$K2="4th+")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="10" stopIfTrue="1">
-      <formula>$K2="2nd"</formula>
+  <conditionalFormatting sqref="E2:E400">
+    <cfRule type="expression" dxfId="10" priority="9" stopIfTrue="1">
+      <formula>$E2="Yes"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L400">
-    <cfRule type="expression" dxfId="7" priority="8" stopIfTrue="1">
-      <formula>$L2="Yes"</formula>
+  <conditionalFormatting sqref="J2:J400">
+    <cfRule type="expression" dxfId="9" priority="10" stopIfTrue="1">
+      <formula>OR($J2="3rd",$J2="4th+")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="11" stopIfTrue="1">
+      <formula>$J2="2nd"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O400">
-    <cfRule type="expression" dxfId="6" priority="1" stopIfTrue="1">
-      <formula>ISNUMBER(SEARCH("HIGH",$O2))</formula>
+    <cfRule type="expression" dxfId="7" priority="1" stopIfTrue="1">
+      <formula>ISNUMBER(SEARCH("URGENT",$O2))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="2" stopIfTrue="1">
       <formula>ISNUMBER(SEARCH("OVERDUE - ESCAL",$O2))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="3" stopIfTrue="1">
       <formula>ISNUMBER(SEARCH("OVERDUE",$O2))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="4" stopIfTrue="1">
       <formula>ISNUMBER(SEARCH("DUE SOON",$O2))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="5" stopIfTrue="1">
-      <formula>ISNUMBER(SEARCH("AWAITING PAYMENT",$O2))</formula>
+    <cfRule type="expression" dxfId="3" priority="5" stopIfTrue="1">
+      <formula>ISNUMBER(SEARCH("SNOOZED",$O2))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="6" stopIfTrue="1">
+      <formula>ISNUMBER(SEARCH("DONE",$O2))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="7" stopIfTrue="1">
+      <formula>ISNUMBER(SEARCH("SET TARGET",$O2))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="8" stopIfTrue="1">
       <formula>ISNUMBER(SEARCH("OK",$O2))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
-      <formula>ISNUMBER(SEARCH("SET DATE",$O2))</formula>
-    </cfRule>
   </conditionalFormatting>
-  <dataValidations count="5">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" sqref="C2:C400" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"Substation Site Enquiry,Turnkey Stage 1,Turnkey Stage 2,Supply Application (&lt;100kW),Upgrading/Downgrading of Supply"</formula1>
+      <formula1>OfficerList</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F400" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"Keyed into SAP,Cost Submitted,Rejected - Pending Resubmission,Engineer Approved,Manager Approved,Charge Issued,Work In Progress,Completed"</formula1>
+    <dataValidation type="list" allowBlank="1" sqref="E2:E400" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H400" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>"10,12,14"</formula1>
+    <dataValidation type="list" allowBlank="1" sqref="G2:G400" xr:uid="{00000000-0002-0000-0000-000002000000}">
+      <formula1>"Not Started,Keyed into SAP,Pending Engineer,Pending Manager,Approved,Rejected - Pending Resubmission,Completed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="K2:K400" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J400" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"1st,2nd,3rd,4th+"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="L2:L400 N2:N400" xr:uid="{00000000-0002-0000-0000-000004000000}">
-      <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1189,56 +1383,119 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="48" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B2" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B3" s="9">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B4" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="9">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
-        <v>52</v>
+        <v>60</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1248,143 +1505,225 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="46" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:A36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="112" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
-        <v>53</v>
+      <c r="A1" s="12" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12"/>
+      <c r="A2" s="13"/>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
-        <v>54</v>
+      <c r="A3" s="12" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
-        <v>55</v>
+      <c r="A4" s="13" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="12"/>
+      <c r="A5" s="13" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
-        <v>56</v>
+      <c r="A6" s="13" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
-        <v>57</v>
-      </c>
+      <c r="A7" s="13"/>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
-        <v>59</v>
+      <c r="A9" s="13" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
-        <v>60</v>
-      </c>
+      <c r="A10" s="13"/>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="s">
-        <v>62</v>
+      <c r="A12" s="13" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" s="12"/>
+      <c r="A13" s="13" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
-        <v>63</v>
-      </c>
+      <c r="A14" s="13"/>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" s="12" t="s">
-        <v>65</v>
+      <c r="A16" s="13" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="12"/>
+      <c r="A17" s="13"/>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
-        <v>66</v>
+      <c r="A18" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="12" t="s">
-        <v>67</v>
+      <c r="A19" s="13" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="12" t="s">
-        <v>68</v>
+      <c r="A20" s="13" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="12"/>
+      <c r="A21" s="13" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
-        <v>69</v>
-      </c>
+      <c r="A22" s="13"/>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="12" t="s">
-        <v>71</v>
+      <c r="A24" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="12" t="s">
-        <v>72</v>
+      <c r="A25" s="13" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="12"/>
+      <c r="A26" s="13" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="11" t="s">
-        <v>73</v>
+      <c r="A27" s="13" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="12" t="s">
-        <v>74</v>
+      <c r="A28" s="13" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" s="12" t="s">
-        <v>75</v>
+      <c r="A29" s="13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="13"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="13"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="13" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
